--- a/AAII_Financials/Yearly/HLLGY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/HLLGY_YR_FIN.xlsx
@@ -302,7 +302,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -344,7 +344,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -653,136 +653,148 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="10" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44712</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44347</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43982</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43616</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43251</v>
       </c>
-      <c r="K7" s="2"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L7" s="2"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>8308100</v>
+      </c>
+      <c r="E8" s="3">
         <v>8792000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>8079600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>6786900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>7800100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>6480700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>7791800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>8231700</v>
       </c>
-      <c r="K8" s="3"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>6542100</v>
+        <v>6489600</v>
       </c>
       <c r="E9" s="3">
+        <v>6724700</v>
+      </c>
+      <c r="F9" s="3">
         <v>6804800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>5221100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>5900800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>4992700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>5766500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>6011500</v>
       </c>
-      <c r="K9" s="3"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>2250000</v>
+        <v>1818500</v>
       </c>
       <c r="E10" s="3">
+        <v>2067400</v>
+      </c>
+      <c r="F10" s="3">
         <v>1274800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1565800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1899300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1488100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2025300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2220200</v>
       </c>
-      <c r="K10" s="3"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -794,35 +806,39 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>974500</v>
+        <v>839300</v>
       </c>
       <c r="E12" s="3">
+        <v>898200</v>
+      </c>
+      <c r="F12" s="3">
         <v>843800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>739600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>819600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>692300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>680800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>662300</v>
       </c>
-      <c r="K12" s="3"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -847,63 +863,72 @@
       <c r="J13" s="3">
         <v>0</v>
       </c>
-      <c r="K13" s="3"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K13" s="3">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>18500</v>
+        <v>-135000</v>
       </c>
       <c r="E14" s="3">
+        <v>-15600</v>
+      </c>
+      <c r="F14" s="3">
         <v>-913200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-38400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-113600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>582300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-7000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>4800</v>
       </c>
-      <c r="K14" s="3"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>463600</v>
+      </c>
+      <c r="E15" s="3">
         <v>472900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>365100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>350400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>393000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>381800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>358600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>477000</v>
       </c>
-      <c r="K15" s="3"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -912,62 +937,69 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>8313000</v>
+        <v>8010200</v>
       </c>
       <c r="E17" s="3">
+        <v>8340400</v>
+      </c>
+      <c r="F17" s="3">
         <v>8408600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6588700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>7420500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>6337100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>7263100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>7633700</v>
       </c>
-      <c r="K17" s="3"/>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3"/>
+    </row>
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>479000</v>
+        <v>297900</v>
       </c>
       <c r="E18" s="3">
+        <v>451600</v>
+      </c>
+      <c r="F18" s="3">
         <v>-191900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>198200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>379700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>143600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>528700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>598000</v>
       </c>
-      <c r="K18" s="3"/>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3"/>
+    </row>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -979,143 +1011,159 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-27900</v>
+        <v>-15200</v>
       </c>
       <c r="E20" s="3">
+        <v>-21200</v>
+      </c>
+      <c r="F20" s="3">
         <v>-94300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-51000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-74200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-39300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-347800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-60400</v>
       </c>
-      <c r="K20" s="3"/>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3"/>
+    </row>
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>979800</v>
+        <v>776800</v>
       </c>
       <c r="E21" s="3">
+        <v>945800</v>
+      </c>
+      <c r="F21" s="3">
         <v>267500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>599700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>846800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>564800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1235100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1135400</v>
       </c>
-      <c r="K21" s="3"/>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3"/>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>65500</v>
+      </c>
+      <c r="E22" s="3">
         <v>83700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>21000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>27400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>31300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>39900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>45800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>52200</v>
       </c>
-      <c r="K22" s="3"/>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3"/>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>427300</v>
+      </c>
+      <c r="E23" s="3">
         <v>438800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>655900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>272500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>547200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-424700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>854100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>618100</v>
       </c>
-      <c r="K23" s="3"/>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3"/>
+    </row>
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>43300</v>
+      </c>
+      <c r="E24" s="3">
         <v>144400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>10900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>75100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>107100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>55200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>151400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>163300</v>
       </c>
-      <c r="K24" s="3"/>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3"/>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1140,63 +1188,72 @@
       <c r="J25" s="3">
         <v>0</v>
       </c>
-      <c r="K25" s="3"/>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K25" s="3">
+        <v>0</v>
+      </c>
+      <c r="L25" s="3"/>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>384000</v>
+      </c>
+      <c r="E26" s="3">
         <v>294400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>645000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>197400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>440100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-479900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>702700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>454800</v>
       </c>
-      <c r="K26" s="3"/>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3"/>
+    </row>
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>365600</v>
+      </c>
+      <c r="E27" s="3">
         <v>291700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>642200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>194500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>438000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-479200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>702300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>453200</v>
       </c>
-      <c r="K27" s="3"/>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3"/>
+    </row>
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1221,9 +1278,12 @@
       <c r="J28" s="3">
         <v>0</v>
       </c>
-      <c r="K28" s="3"/>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K28" s="3">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3"/>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1248,9 +1308,12 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3"/>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3"/>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1275,9 +1338,12 @@
       <c r="J30" s="3">
         <v>0</v>
       </c>
-      <c r="K30" s="3"/>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K30" s="3">
+        <v>0</v>
+      </c>
+      <c r="L30" s="3"/>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1302,63 +1368,72 @@
       <c r="J31" s="3">
         <v>0</v>
       </c>
-      <c r="K31" s="3"/>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K31" s="3">
+        <v>0</v>
+      </c>
+      <c r="L31" s="3"/>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>27900</v>
+        <v>15200</v>
       </c>
       <c r="E32" s="3">
+        <v>21200</v>
+      </c>
+      <c r="F32" s="3">
         <v>94300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>51000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>74200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>39300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>347800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>60400</v>
       </c>
-      <c r="K32" s="3"/>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3"/>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>365600</v>
+      </c>
+      <c r="E33" s="3">
         <v>291700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>642200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>194500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>438000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-479200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>702300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>453200</v>
       </c>
-      <c r="K33" s="3"/>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3"/>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1383,68 +1458,77 @@
       <c r="J34" s="3">
         <v>0</v>
       </c>
-      <c r="K34" s="3"/>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K34" s="3">
+        <v>0</v>
+      </c>
+      <c r="L34" s="3"/>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>365600</v>
+      </c>
+      <c r="E35" s="3">
         <v>291700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>642200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>194500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>438000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-479200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>702300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>453200</v>
       </c>
-      <c r="K35" s="3"/>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3"/>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44712</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44347</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43982</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43616</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43251</v>
       </c>
-      <c r="K38" s="2"/>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L38" s="2"/>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -1456,8 +1540,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -1469,35 +1554,39 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
-        <v>1205300</v>
+        <v>1341200</v>
       </c>
       <c r="E41" s="3">
+        <v>1210400</v>
+      </c>
+      <c r="F41" s="3">
         <v>1374300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>618100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1197600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1337200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>977300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>802400</v>
       </c>
-      <c r="K41" s="3"/>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L41" s="3"/>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
@@ -1505,215 +1594,239 @@
         <v>109800</v>
       </c>
       <c r="E42" s="3">
+        <v>109800</v>
+      </c>
+      <c r="F42" s="3">
         <v>165400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>425600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>534400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>479200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>597400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>375500</v>
       </c>
-      <c r="K42" s="3"/>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3"/>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>1285300</v>
+      </c>
+      <c r="E43" s="3">
         <v>1342300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1318000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1382700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1415300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>896000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1395200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1476900</v>
       </c>
-      <c r="K43" s="3"/>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L43" s="3"/>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>1157600</v>
+      </c>
+      <c r="E44" s="3">
         <v>1243000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1248500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1219200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1100900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>980000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>903200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>887800</v>
       </c>
-      <c r="K44" s="3"/>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3"/>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>252200</v>
+        <v>134000</v>
       </c>
       <c r="E45" s="3">
+        <v>247200</v>
+      </c>
+      <c r="F45" s="3">
         <v>173800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>118600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>95300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>111200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>136200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>62700</v>
       </c>
-      <c r="K45" s="3"/>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L45" s="3"/>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>4028000</v>
+      </c>
+      <c r="E46" s="3">
         <v>4152700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4280000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3764200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4343500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3803700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4009300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3644600</v>
       </c>
-      <c r="K46" s="3"/>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L46" s="3"/>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>180000</v>
+      </c>
+      <c r="E47" s="3">
         <v>223300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>317300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>368400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>320900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>252400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>347600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>375900</v>
       </c>
-      <c r="K47" s="3"/>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L47" s="3"/>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>2405500</v>
+      </c>
+      <c r="E48" s="3">
         <v>2484300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2423100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2099000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2092500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1771500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2164400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2325100</v>
       </c>
-      <c r="K48" s="3"/>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L48" s="3"/>
+    </row>
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>80500</v>
+      </c>
+      <c r="E49" s="3">
         <v>48900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>43600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>42800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>46500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>46300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>95200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>110400</v>
       </c>
-      <c r="K49" s="3"/>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L49" s="3"/>
+    </row>
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -1738,9 +1851,12 @@
       <c r="J50" s="3">
         <v>0</v>
       </c>
-      <c r="K50" s="3"/>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K50" s="3">
+        <v>0</v>
+      </c>
+      <c r="L50" s="3"/>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -1765,36 +1881,42 @@
       <c r="J51" s="3">
         <v>0</v>
       </c>
-      <c r="K51" s="3"/>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K51" s="3">
+        <v>0</v>
+      </c>
+      <c r="L51" s="3"/>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>83000</v>
+      </c>
+      <c r="E52" s="3">
         <v>71200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>63800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>49700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>68700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>19200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>13200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>19000</v>
       </c>
-      <c r="K52" s="3"/>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L52" s="3"/>
+    </row>
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -1819,36 +1941,42 @@
       <c r="J53" s="3">
         <v>0</v>
       </c>
-      <c r="K53" s="3"/>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K53" s="3">
+        <v>0</v>
+      </c>
+      <c r="L53" s="3"/>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>7747400</v>
+      </c>
+      <c r="E54" s="3">
         <v>7805500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7799000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6914500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7407000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6328800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>7144800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6903600</v>
       </c>
-      <c r="K54" s="3"/>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L54" s="3"/>
+    </row>
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -1860,8 +1988,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -1873,170 +2002,189 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>1416400</v>
+      </c>
+      <c r="E57" s="3">
         <v>1332100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1279900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>986900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>991500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>540400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>757000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>710800</v>
       </c>
-      <c r="K57" s="3"/>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L57" s="3"/>
+    </row>
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>168300</v>
+      </c>
+      <c r="E58" s="3">
         <v>480000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>271300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>231300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>95300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>559900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>648800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>49000</v>
       </c>
-      <c r="K58" s="3"/>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="3"/>
+    </row>
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>885900</v>
+      </c>
+      <c r="E59" s="3">
         <v>891200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>821500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>709500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>784300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>622700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>676100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>888000</v>
       </c>
-      <c r="K59" s="3"/>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L59" s="3"/>
+    </row>
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>2714100</v>
+      </c>
+      <c r="E60" s="3">
         <v>2964100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2569100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2187700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2165900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1956400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2351900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1948200</v>
       </c>
-      <c r="K60" s="3"/>
-    </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L60" s="3"/>
+    </row>
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>1077500</v>
+      </c>
+      <c r="E61" s="3">
         <v>928900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1255700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1259400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1516800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1428100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>876300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1359300</v>
       </c>
-      <c r="K61" s="3"/>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="3"/>
+    </row>
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>281900</v>
+      </c>
+      <c r="E62" s="3">
         <v>348400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>398600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>164700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>246500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>178300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>186200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>189600</v>
       </c>
-      <c r="K62" s="3"/>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L62" s="3"/>
+    </row>
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -2061,9 +2209,12 @@
       <c r="J63" s="3">
         <v>0</v>
       </c>
-      <c r="K63" s="3"/>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K63" s="3">
+        <v>0</v>
+      </c>
+      <c r="L63" s="3"/>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -2088,9 +2239,12 @@
       <c r="J64" s="3">
         <v>0</v>
       </c>
-      <c r="K64" s="3"/>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K64" s="3">
+        <v>0</v>
+      </c>
+      <c r="L64" s="3"/>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -2115,36 +2269,42 @@
       <c r="J65" s="3">
         <v>0</v>
       </c>
-      <c r="K65" s="3"/>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K65" s="3">
+        <v>0</v>
+      </c>
+      <c r="L65" s="3"/>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>4385500</v>
+      </c>
+      <c r="E66" s="3">
         <v>4602300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4527600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3975800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4398600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3986800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3835800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4014200</v>
       </c>
-      <c r="K66" s="3"/>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L66" s="3"/>
+    </row>
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -2156,8 +2316,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -2182,9 +2343,12 @@
       <c r="J68" s="3">
         <v>0</v>
       </c>
-      <c r="K68" s="3"/>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K68" s="3">
+        <v>0</v>
+      </c>
+      <c r="L68" s="3"/>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -2209,9 +2373,12 @@
       <c r="J69" s="3">
         <v>0</v>
       </c>
-      <c r="K69" s="3"/>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K69" s="3">
+        <v>0</v>
+      </c>
+      <c r="L69" s="3"/>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -2236,9 +2403,12 @@
       <c r="J70" s="3">
         <v>0</v>
       </c>
-      <c r="K70" s="3"/>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3"/>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -2263,36 +2433,42 @@
       <c r="J71" s="3">
         <v>0</v>
       </c>
-      <c r="K71" s="3"/>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K71" s="3">
+        <v>0</v>
+      </c>
+      <c r="L71" s="3"/>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>2957600</v>
+      </c>
+      <c r="E72" s="3">
         <v>2854600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2819800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2513100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2772800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2122900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3023900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2521700</v>
       </c>
-      <c r="K72" s="3"/>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L72" s="3"/>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -2317,9 +2493,12 @@
       <c r="J73" s="3">
         <v>0</v>
       </c>
-      <c r="K73" s="3"/>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K73" s="3">
+        <v>0</v>
+      </c>
+      <c r="L73" s="3"/>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -2344,9 +2523,12 @@
       <c r="J74" s="3">
         <v>0</v>
       </c>
-      <c r="K74" s="3"/>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K74" s="3">
+        <v>0</v>
+      </c>
+      <c r="L74" s="3"/>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -2371,36 +2553,42 @@
       <c r="J75" s="3">
         <v>0</v>
       </c>
-      <c r="K75" s="3"/>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K75" s="3">
+        <v>0</v>
+      </c>
+      <c r="L75" s="3"/>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>3313400</v>
+      </c>
+      <c r="E76" s="3">
         <v>3198200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3267400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2935600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3006200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2340700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3306100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2884900</v>
       </c>
-      <c r="K76" s="3"/>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L76" s="3"/>
+    </row>
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -2425,68 +2613,77 @@
       <c r="J77" s="3">
         <v>0</v>
       </c>
-      <c r="K77" s="3"/>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K77" s="3">
+        <v>0</v>
+      </c>
+      <c r="L77" s="3"/>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44712</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44347</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43982</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43616</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43251</v>
       </c>
-      <c r="K80" s="2"/>
-    </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L80" s="2"/>
+    </row>
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>365600</v>
+      </c>
+      <c r="E81" s="3">
         <v>291700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>642200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>194500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>438000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-479200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>702300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>453200</v>
       </c>
-      <c r="K81" s="3"/>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3"/>
+    </row>
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -2498,35 +2695,39 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>484300</v>
+      </c>
+      <c r="E83" s="3">
         <v>496400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>393000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>369700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>410100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>400900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>370800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>459400</v>
       </c>
-      <c r="K83" s="3"/>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3"/>
+    </row>
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -2551,9 +2752,12 @@
       <c r="J84" s="3">
         <v>0</v>
       </c>
-      <c r="K84" s="3"/>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K84" s="3">
+        <v>0</v>
+      </c>
+      <c r="L84" s="3"/>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -2578,9 +2782,12 @@
       <c r="J85" s="3">
         <v>0</v>
       </c>
-      <c r="K85" s="3"/>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K85" s="3">
+        <v>0</v>
+      </c>
+      <c r="L85" s="3"/>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -2605,9 +2812,12 @@
       <c r="J86" s="3">
         <v>0</v>
       </c>
-      <c r="K86" s="3"/>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K86" s="3">
+        <v>0</v>
+      </c>
+      <c r="L86" s="3"/>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -2632,9 +2842,12 @@
       <c r="J87" s="3">
         <v>0</v>
       </c>
-      <c r="K87" s="3"/>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K87" s="3">
+        <v>0</v>
+      </c>
+      <c r="L87" s="3"/>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -2659,36 +2872,42 @@
       <c r="J88" s="3">
         <v>0</v>
       </c>
-      <c r="K88" s="3"/>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K88" s="3">
+        <v>0</v>
+      </c>
+      <c r="L88" s="3"/>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>884300</v>
+      </c>
+      <c r="E89" s="3">
         <v>912700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1146000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>313800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>860500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>706800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>846000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>962900</v>
       </c>
-      <c r="K89" s="3"/>
-    </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L89" s="3"/>
+    </row>
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -2700,35 +2919,39 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-471800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-513300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-330300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-467300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-609500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-452500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-489700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-598300</v>
       </c>
-      <c r="K91" s="3"/>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L91" s="3"/>
+    </row>
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -2753,9 +2976,12 @@
       <c r="J92" s="3">
         <v>0</v>
       </c>
-      <c r="K92" s="3"/>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K92" s="3">
+        <v>0</v>
+      </c>
+      <c r="L92" s="3"/>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -2780,36 +3006,42 @@
       <c r="J93" s="3">
         <v>0</v>
       </c>
-      <c r="K93" s="3"/>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K93" s="3">
+        <v>0</v>
+      </c>
+      <c r="L93" s="3"/>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-476600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-595200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>233500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-603600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-543600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-309800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-415400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-739600</v>
       </c>
-      <c r="K94" s="3"/>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L94" s="3"/>
+    </row>
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -2821,35 +3053,39 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
+        <v>84200</v>
+      </c>
+      <c r="E96" s="3">
         <v>354000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>58200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>114700</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
       <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
         <v>129700</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>130000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>119200</v>
       </c>
-      <c r="K96" s="3"/>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3"/>
+    </row>
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -2874,9 +3110,12 @@
       <c r="J97" s="3">
         <v>0</v>
       </c>
-      <c r="K97" s="3"/>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K97" s="3">
+        <v>0</v>
+      </c>
+      <c r="L97" s="3"/>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -2901,9 +3140,12 @@
       <c r="J98" s="3">
         <v>0</v>
       </c>
-      <c r="K98" s="3"/>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K98" s="3">
+        <v>0</v>
+      </c>
+      <c r="L98" s="3"/>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -2928,88 +3170,100 @@
       <c r="J99" s="3">
         <v>0</v>
       </c>
-      <c r="K99" s="3"/>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K99" s="3">
+        <v>0</v>
+      </c>
+      <c r="L99" s="3"/>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-242700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-518700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-37600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-160100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-590200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-26400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-220100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-330800</v>
       </c>
-      <c r="K100" s="3"/>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L100" s="3"/>
+    </row>
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E101" s="3">
         <v>-14800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-8600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>17200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-8200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-4000</v>
       </c>
-      <c r="K101" s="3"/>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3"/>
+    </row>
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>170400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-216100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1333400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-432700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-273000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>362500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>210200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-111600</v>
       </c>
-      <c r="K102" s="3"/>
+      <c r="L102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/HLLGY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/HLLGY_YR_FIN.xlsx
@@ -653,148 +653,160 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="12" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44712</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44347</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43982</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43616</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43251</v>
       </c>
-      <c r="L7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>9231100</v>
+      </c>
+      <c r="E8" s="3">
         <v>8308100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>8792000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>8079600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>6786900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>7800100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>6480700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>7791800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>8231700</v>
       </c>
-      <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>6489600</v>
+        <v>7067800</v>
       </c>
       <c r="E9" s="3">
+        <v>6386200</v>
+      </c>
+      <c r="F9" s="3">
         <v>6724700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>6804800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>5221100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>5900800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>4992700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>5766500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6011500</v>
       </c>
-      <c r="L9" s="3"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1818500</v>
+        <v>2163300</v>
       </c>
       <c r="E10" s="3">
+        <v>1921900</v>
+      </c>
+      <c r="F10" s="3">
         <v>2067400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1274800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1565800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1899300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1488100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2025300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2220200</v>
       </c>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -807,38 +819,42 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>839300</v>
+        <v>861000</v>
       </c>
       <c r="E12" s="3">
+        <v>831600</v>
+      </c>
+      <c r="F12" s="3">
         <v>898200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>843800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>739600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>819600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>692300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>680800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>662300</v>
       </c>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -866,69 +882,78 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-      <c r="L13" s="3"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>-135000</v>
+        <v>262900</v>
       </c>
       <c r="E14" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="F14" s="3">
         <v>-15600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-913200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-38400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-113600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>582300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-7000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>4800</v>
       </c>
-      <c r="L14" s="3"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>504100</v>
+      </c>
+      <c r="E15" s="3">
         <v>463600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>472900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>365100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>350400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>393000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>381800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>358600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>477000</v>
       </c>
-      <c r="L15" s="3"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -938,68 +963,75 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>8010200</v>
+        <v>8648500</v>
       </c>
       <c r="E17" s="3">
+        <v>7886700</v>
+      </c>
+      <c r="F17" s="3">
         <v>8340400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>8408600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>6588700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>7420500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6337100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>7263100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7633700</v>
       </c>
-      <c r="L17" s="3"/>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>297900</v>
+        <v>582600</v>
       </c>
       <c r="E18" s="3">
+        <v>421400</v>
+      </c>
+      <c r="F18" s="3">
         <v>451600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-191900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>198200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>379700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>143600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>528700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>598000</v>
       </c>
-      <c r="L18" s="3"/>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1012,158 +1044,174 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-20200</v>
+      </c>
+      <c r="E20" s="3">
         <v>-15200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-21200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-94300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-51000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-74200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-39300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-347800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-60400</v>
       </c>
-      <c r="L20" s="3"/>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>776800</v>
+        <v>1106900</v>
       </c>
       <c r="E21" s="3">
+        <v>900200</v>
+      </c>
+      <c r="F21" s="3">
         <v>945800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>267500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>599700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>846800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>564800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1235100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1135400</v>
       </c>
-      <c r="L21" s="3"/>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>66100</v>
+      </c>
+      <c r="E22" s="3">
         <v>65500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>83700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>21000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>27400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>31300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>39900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>45800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>52200</v>
       </c>
-      <c r="L22" s="3"/>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>302800</v>
+      </c>
+      <c r="E23" s="3">
         <v>427300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>438800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>655900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>272500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>547200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-424700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>854100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>618100</v>
       </c>
-      <c r="L23" s="3"/>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M23" s="3"/>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>193900</v>
+      </c>
+      <c r="E24" s="3">
         <v>43300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>144400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>10900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>75100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>107100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>55200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>151400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>163300</v>
       </c>
-      <c r="L24" s="3"/>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3"/>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1191,69 +1239,78 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-      <c r="L25" s="3"/>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3"/>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>108800</v>
+      </c>
+      <c r="E26" s="3">
         <v>384000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>294400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>645000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>197400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>440100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-479900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>702700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>454800</v>
       </c>
-      <c r="L26" s="3"/>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="3"/>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>97800</v>
+      </c>
+      <c r="E27" s="3">
         <v>365600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>291700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>642200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>194500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>438000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-479200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>702300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>453200</v>
       </c>
-      <c r="L27" s="3"/>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="3"/>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1281,9 +1338,12 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-      <c r="L28" s="3"/>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3"/>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1311,9 +1371,12 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3"/>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3"/>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1341,9 +1404,12 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-      <c r="L30" s="3"/>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3"/>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1371,69 +1437,78 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-      <c r="L31" s="3"/>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3"/>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>20200</v>
+      </c>
+      <c r="E32" s="3">
         <v>15200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>21200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>94300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>51000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>74200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>39300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>347800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>60400</v>
       </c>
-      <c r="L32" s="3"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3"/>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>97800</v>
+      </c>
+      <c r="E33" s="3">
         <v>365600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>291700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>642200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>194500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>438000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-479200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>702300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>453200</v>
       </c>
-      <c r="L33" s="3"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="3"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1461,74 +1536,83 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-      <c r="L34" s="3"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>97800</v>
+      </c>
+      <c r="E35" s="3">
         <v>365600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>291700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>642200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>194500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>438000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-479200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>702300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>453200</v>
       </c>
-      <c r="L35" s="3"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="3"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44712</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44347</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43982</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43616</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43251</v>
       </c>
-      <c r="L38" s="2"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -1541,8 +1625,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -1555,278 +1640,306 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>1649000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1341200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1210400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1374300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>618100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1197600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1337200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>977300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>802400</v>
       </c>
-      <c r="L41" s="3"/>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M41" s="3"/>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
-        <v>109800</v>
+        <v>108300</v>
       </c>
       <c r="E42" s="3">
         <v>109800</v>
       </c>
       <c r="F42" s="3">
+        <v>109800</v>
+      </c>
+      <c r="G42" s="3">
         <v>165400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>425600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>534400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>479200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>597400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>375500</v>
       </c>
-      <c r="L42" s="3"/>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M42" s="3"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>1305400</v>
+      </c>
+      <c r="E43" s="3">
         <v>1285300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1342300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1318000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1382700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1415300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>896000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1395200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1476900</v>
       </c>
-      <c r="L43" s="3"/>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M43" s="3"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>1325900</v>
+      </c>
+      <c r="E44" s="3">
         <v>1157600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1243000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1248500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1219200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1100900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>980000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>903200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>887800</v>
       </c>
-      <c r="L44" s="3"/>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M44" s="3"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>191400</v>
+      </c>
+      <c r="E45" s="3">
         <v>134000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>247200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>173800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>118600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>95300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>111200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>136200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>62700</v>
       </c>
-      <c r="L45" s="3"/>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M45" s="3"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>4579900</v>
+      </c>
+      <c r="E46" s="3">
         <v>4028000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4152700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4280000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3764200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4343500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3803700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4009300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3644600</v>
       </c>
-      <c r="L46" s="3"/>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M46" s="3"/>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>195400</v>
+      </c>
+      <c r="E47" s="3">
         <v>180000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>223300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>317300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>368400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>320900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>252400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>347600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>375900</v>
       </c>
-      <c r="L47" s="3"/>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M47" s="3"/>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>2452200</v>
+      </c>
+      <c r="E48" s="3">
         <v>2405500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2484300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2423100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2099000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2092500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1771500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2164400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2325100</v>
       </c>
-      <c r="L48" s="3"/>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M48" s="3"/>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>82500</v>
+      </c>
+      <c r="E49" s="3">
         <v>80500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>48900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>43600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>42800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>46500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>46300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>95200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>110400</v>
       </c>
-      <c r="L49" s="3"/>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M49" s="3"/>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -1854,9 +1967,12 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-      <c r="L50" s="3"/>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3"/>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -1884,39 +2000,45 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-      <c r="L51" s="3"/>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3"/>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>142900</v>
+      </c>
+      <c r="E52" s="3">
         <v>83000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>71200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>63800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>49700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>68700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>19200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>13200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>19000</v>
       </c>
-      <c r="L52" s="3"/>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M52" s="3"/>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -1944,39 +2066,45 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-      <c r="L53" s="3"/>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3"/>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>8600900</v>
+      </c>
+      <c r="E54" s="3">
         <v>7747400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7805500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7799000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6914500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>7407000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6328800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7144800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6903600</v>
       </c>
-      <c r="L54" s="3"/>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M54" s="3"/>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -1989,8 +2117,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -2003,188 +2132,207 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>1722200</v>
+      </c>
+      <c r="E57" s="3">
         <v>1416400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1332100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1279900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>986900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>991500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>540400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>757000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>710800</v>
       </c>
-      <c r="L57" s="3"/>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M57" s="3"/>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>243000</v>
+      </c>
+      <c r="E58" s="3">
         <v>168300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>480000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>271300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>231300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>95300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>559900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>648800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>49000</v>
       </c>
-      <c r="L58" s="3"/>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M58" s="3"/>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>907600</v>
+      </c>
+      <c r="E59" s="3">
         <v>885900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>891200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>821500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>709500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>784300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>622700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>676100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>888000</v>
       </c>
-      <c r="L59" s="3"/>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M59" s="3"/>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>3184200</v>
+      </c>
+      <c r="E60" s="3">
         <v>2714100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2964100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2569100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2187700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2165900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1956400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2351900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1948200</v>
       </c>
-      <c r="L60" s="3"/>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M60" s="3"/>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>1087600</v>
+      </c>
+      <c r="E61" s="3">
         <v>1077500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>928900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1255700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1259400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1516800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1428100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>876300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1359300</v>
       </c>
-      <c r="L61" s="3"/>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M61" s="3"/>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>264200</v>
+      </c>
+      <c r="E62" s="3">
         <v>281900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>348400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>398600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>164700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>246500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>178300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>186200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>189600</v>
       </c>
-      <c r="L62" s="3"/>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M62" s="3"/>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -2212,9 +2360,12 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-      <c r="L63" s="3"/>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3"/>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -2242,9 +2393,12 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-      <c r="L64" s="3"/>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3"/>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -2272,39 +2426,45 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-      <c r="L65" s="3"/>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3"/>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>4927900</v>
+      </c>
+      <c r="E66" s="3">
         <v>4385500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4602300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4527600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3975800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4398600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3986800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3835800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4014200</v>
       </c>
-      <c r="L66" s="3"/>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M66" s="3"/>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -2317,8 +2477,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -2346,9 +2507,12 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-      <c r="L68" s="3"/>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3"/>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -2376,9 +2540,12 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-      <c r="L69" s="3"/>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3"/>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -2406,9 +2573,12 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-      <c r="L70" s="3"/>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3"/>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -2436,39 +2606,45 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-      <c r="L71" s="3"/>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3"/>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>3323800</v>
+      </c>
+      <c r="E72" s="3">
         <v>2957600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2854600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2819800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2513100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2772800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2122900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3023900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2521700</v>
       </c>
-      <c r="L72" s="3"/>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M72" s="3"/>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -2496,9 +2672,12 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-      <c r="L73" s="3"/>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3"/>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -2526,9 +2705,12 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-      <c r="L74" s="3"/>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3"/>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -2556,39 +2738,45 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-      <c r="L75" s="3"/>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3"/>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>3617700</v>
+      </c>
+      <c r="E76" s="3">
         <v>3313400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3198200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3267400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2935600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3006200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2340700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3306100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2884900</v>
       </c>
-      <c r="L76" s="3"/>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M76" s="3"/>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -2616,74 +2804,83 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-      <c r="L77" s="3"/>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3"/>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44712</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44347</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43982</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43616</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43251</v>
       </c>
-      <c r="L80" s="2"/>
-    </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M80" s="2"/>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>97800</v>
+      </c>
+      <c r="E81" s="3">
         <v>365600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>291700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>642200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>194500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>438000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-479200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>702300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>453200</v>
       </c>
-      <c r="L81" s="3"/>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M81" s="3"/>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -2696,38 +2893,42 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>531800</v>
+      </c>
+      <c r="E83" s="3">
         <v>484300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>496400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>393000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>369700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>410100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>400900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>370800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>459400</v>
       </c>
-      <c r="L83" s="3"/>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M83" s="3"/>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -2755,9 +2956,12 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-      <c r="L84" s="3"/>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3"/>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -2785,9 +2989,12 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-      <c r="L85" s="3"/>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3"/>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -2815,9 +3022,12 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-      <c r="L86" s="3"/>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3"/>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -2845,9 +3055,12 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-      <c r="L87" s="3"/>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3"/>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -2875,39 +3088,45 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-      <c r="L88" s="3"/>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3"/>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>1070600</v>
+      </c>
+      <c r="E89" s="3">
         <v>884300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>912700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1146000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>313800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>860500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>706800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>846000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>962900</v>
       </c>
-      <c r="L89" s="3"/>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M89" s="3"/>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -2920,38 +3139,42 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-419800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-471800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-513300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-330300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-467300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-609500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-452500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-489700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-598300</v>
       </c>
-      <c r="L91" s="3"/>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M91" s="3"/>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -2979,9 +3202,12 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-      <c r="L92" s="3"/>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3"/>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -3009,39 +3235,45 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-      <c r="L93" s="3"/>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3"/>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-701500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-476600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-595200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>233500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-603600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-543600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-309800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-415400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-739600</v>
       </c>
-      <c r="L94" s="3"/>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M94" s="3"/>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -3054,38 +3286,42 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
+        <v>130400</v>
+      </c>
+      <c r="E96" s="3">
         <v>84200</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>354000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>58200</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>114700</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>129700</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>130000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>119200</v>
       </c>
-      <c r="L96" s="3"/>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M96" s="3"/>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -3113,9 +3349,12 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-      <c r="L97" s="3"/>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3"/>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -3143,9 +3382,12 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-      <c r="L98" s="3"/>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3"/>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -3173,97 +3415,109 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-      <c r="L99" s="3"/>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3"/>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-196800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-242700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-518700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-37600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-160100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-590200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-26400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-220100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-330800</v>
       </c>
-      <c r="L100" s="3"/>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M100" s="3"/>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>-44200</v>
+      </c>
+      <c r="E101" s="3">
         <v>5500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-14800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-8600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>17200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-8200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-4000</v>
       </c>
-      <c r="L101" s="3"/>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M101" s="3"/>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>128200</v>
+      </c>
+      <c r="E102" s="3">
         <v>170400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-216100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1333400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-432700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-273000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>362500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>210200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-111600</v>
       </c>
-      <c r="L102" s="3"/>
+      <c r="M102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
